--- a/Agentic_AI/Senior_Python_Backend_Hiring_Companies.xlsx
+++ b/Agentic_AI/Senior_Python_Backend_Hiring_Companies.xlsx
@@ -8,11 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hiring Companies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Search Links" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hiring Companies'!$A$1:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority'!$A$3:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +57,24 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -88,8 +107,29 @@
         <bgColor rgb="FFFCE8B2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E7FB"/>
+        <bgColor rgb="FFD9E7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -111,11 +151,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -143,6 +197,47 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -521,6 +616,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,6 +670,11 @@
           <t>Mode</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Exp Fit (4 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -623,6 +724,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -672,6 +778,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -721,6 +832,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -770,6 +886,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -819,6 +940,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -868,6 +994,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -913,6 +1044,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -962,6 +1098,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1007,6 +1148,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1056,6 +1202,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1105,6 +1256,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1154,6 +1310,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1203,6 +1364,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1248,6 +1414,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1297,6 +1468,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1346,6 +1522,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1395,6 +1576,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1444,6 +1630,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1493,6 +1684,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1542,6 +1738,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1591,6 +1792,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1640,6 +1846,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>Below (jr/intern)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1689,6 +1900,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1738,6 +1954,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1787,6 +2008,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1836,6 +2062,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1881,6 +2112,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1930,6 +2166,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K29" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1975,6 +2216,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2020,6 +2266,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2065,6 +2316,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2114,6 +2370,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2159,6 +2420,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2204,6 +2470,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2249,6 +2520,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2294,6 +2570,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2339,6 +2620,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2388,6 +2674,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2437,6 +2728,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2482,6 +2778,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2527,6 +2828,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2572,6 +2878,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K43" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2621,6 +2932,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K44" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2666,6 +2982,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K45" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2715,6 +3036,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K46" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2760,6 +3086,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K47" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2805,6 +3136,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2850,6 +3186,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K49" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2895,6 +3236,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2944,6 +3290,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K51" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2989,6 +3340,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3034,6 +3390,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3079,6 +3440,11 @@
           <t>Varies</t>
         </is>
       </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3128,6 +3494,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -3177,6 +3548,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -3226,6 +3602,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -3275,6 +3656,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
@@ -3324,6 +3710,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="n">
@@ -3373,6 +3764,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -3422,6 +3818,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -3471,6 +3872,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -3520,6 +3926,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -3569,6 +3980,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K64" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -3618,6 +4034,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -3667,6 +4088,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -3716,6 +4142,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -3765,6 +4196,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="n">
@@ -3814,6 +4250,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="n">
@@ -3863,6 +4304,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K70" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
@@ -3912,6 +4358,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -3961,6 +4412,11 @@
           <t>Remote</t>
         </is>
       </c>
+      <c r="K72" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
@@ -4010,6 +4466,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="n">
@@ -4059,6 +4520,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
@@ -4108,6 +4574,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K75" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
@@ -4157,6 +4628,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K76" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
@@ -4206,6 +4682,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
@@ -4255,6 +4736,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K78" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="n">
@@ -4304,6 +4790,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="n">
@@ -4353,6 +4844,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
@@ -4402,6 +4898,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="n">
@@ -4451,6 +4952,11 @@
           <t>Onsite/Hybrid</t>
         </is>
       </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="n">
@@ -4500,6 +5006,11 @@
           <t>Onsite</t>
         </is>
       </c>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="n">
@@ -4547,6 +5058,1577 @@
       <c r="J84" s="9" t="inlineStr">
         <is>
           <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K84" s="16" t="inlineStr">
+        <is>
+          <t>Stretch (lead/8+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>Solutionchamps Technologies</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer (React Exposure)</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G85" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aajxp9vgdy6r","Apply")</f>
+        <v/>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — exact title</t>
+        </is>
+      </c>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>Valiant Systems</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>Chennai (Porur)</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G86" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa89qvp66ggl","Apply")</f>
+        <v/>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai</t>
+        </is>
+      </c>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K86" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>Roanuz</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G87" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aazk7dyflt8g","Apply")</f>
+        <v/>
+      </c>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — product (cricket API)</t>
+        </is>
+      </c>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K87" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>AEVEVO Technology</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>Senior React/Django Developer</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G88" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aayqpws9vd8d","Apply")</f>
+        <v/>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — Django, freshest</t>
+        </is>
+      </c>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Senior PySpark Developer</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G89" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aasm9c6lhfyl","Apply")</f>
+        <v/>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — MNC, data eng</t>
+        </is>
+      </c>
+      <c r="J89" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K89" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>AI/ML Computational Science Sr Analyst</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G90" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aakqq4hygdvt","Apply")</f>
+        <v/>
+      </c>
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — AI/ML</t>
+        </is>
+      </c>
+      <c r="J90" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K90" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>10decoders</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer — AI-Enabled App Dev</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G91" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aajdjyjnmdvw","Apply")</f>
+        <v/>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Chennai — AI apps</t>
+        </is>
+      </c>
+      <c r="J91" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K91" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>InterProducTec Virtual Labs</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Sr. Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>Navi Mumbai (Airoli)</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G92" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aazghkbhv4s6","Apply")</f>
+        <v/>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai — exact title</t>
+        </is>
+      </c>
+      <c r="J92" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>DSMD.inc</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G93" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa2cvvqpwhy2","Apply")</f>
+        <v/>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai</t>
+        </is>
+      </c>
+      <c r="J93" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K93" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>Rhosigma Engineering</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python/Django Developer</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>Thane, Mumbai</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G94" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aamj229l4qh6","Apply")</f>
+        <v/>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai — Django</t>
+        </is>
+      </c>
+      <c r="J94" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>Infomanav</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer (Django)</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>Mumbai / Nashik</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G95" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aapyv4twsn8x","Apply")</f>
+        <v/>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai — Django</t>
+        </is>
+      </c>
+      <c r="J95" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K95" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Proximus</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G96" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aak6ksy7lxsy","Apply")</f>
+        <v/>
+      </c>
+      <c r="H96" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai</t>
+        </is>
+      </c>
+      <c r="J96" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K96" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>The Propertist</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G97" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aampsr7ls8fd","Apply")</f>
+        <v/>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai</t>
+        </is>
+      </c>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>Gray Matrix</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>Python Developers</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G98" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aalzhr2ydzxr","Apply")</f>
+        <v/>
+      </c>
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Mumbai</t>
+        </is>
+      </c>
+      <c r="J98" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>Python, FastAPI — Agentic AI Platforms</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G99" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aaldrrkds7tm","Apply")</f>
+        <v/>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Kolkata — FastAPI + Agentic AI (strong fit)</t>
+        </is>
+      </c>
+      <c r="J99" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>Senior Associate — Python Developer (GCC Advisory)</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G100" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aak828bhv2sl","Apply")</f>
+        <v/>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Kolkata — Big-4 brand</t>
+        </is>
+      </c>
+      <c r="J100" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>Proclivity Digitech</t>
+        </is>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; AWS Claude Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G101" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa8y7p8r87zy","Apply")</f>
+        <v/>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Kolkata — Claude/AWS, agentic-AI fit</t>
+        </is>
+      </c>
+      <c r="J101" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>Techno Wise (India)</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>Python Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G102" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aamwm7dndjnp","Apply")</f>
+        <v/>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Kolkata</t>
+        </is>
+      </c>
+      <c r="J102" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>Team HR</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G103" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa9xxlv6p6cv","Apply")</f>
+        <v/>
+      </c>
+      <c r="H103" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K103" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>TOPS Infosolutions</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G104" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aawmp77n6syr","Apply")</f>
+        <v/>
+      </c>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J104" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>WeblineIndia</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer (Python + React)</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G105" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa2nrmnt8kkl","Apply")</f>
+        <v/>
+      </c>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Ahmedabad</t>
+        </is>
+      </c>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K105" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>ManekTech</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>Sr. AIML Developer</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G106" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aawcfs6264fd","Apply")</f>
+        <v/>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Ahmedabad — AI/ML</t>
+        </is>
+      </c>
+      <c r="J106" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K106" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>Auriga</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>SDE II - Python Engineer</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G107" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aadkshlzbc7p","Apply")</f>
+        <v/>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Jaipur — mid/senior SDE</t>
+        </is>
+      </c>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>Orangedatatech</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>Indore</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G108" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aam7xnvzwddq","Apply")</f>
+        <v/>
+      </c>
+      <c r="H108" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Indore</t>
+        </is>
+      </c>
+      <c r="J108" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>Custom Software Engineer</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>Indore</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G109" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aanwhkzkgs28","Apply")</f>
+        <v/>
+      </c>
+      <c r="H109" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Indore</t>
+        </is>
+      </c>
+      <c r="J109" s="13" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="K109" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>Shastika Global Impex</t>
+        </is>
+      </c>
+      <c r="C110" s="13" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G110" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aa9jsx4hmvzt","Apply")</f>
+        <v/>
+      </c>
+      <c r="H110" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Coimbatore</t>
+        </is>
+      </c>
+      <c r="J110" s="13" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>HelixBeat</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
+        <is>
+          <t>Senior Engineer — Python, Django/FastAPI, Airflow/PySpark</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G111" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aaywk8glgdcn","Apply")</f>
+        <v/>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Remote — exact stack match</t>
+        </is>
+      </c>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="K111" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="13" t="inlineStr">
+        <is>
+          <t>Immersive Infotech</t>
+        </is>
+      </c>
+      <c r="C112" s="13" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G112" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aafcbjmfzrcx","Apply")</f>
+        <v/>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Remote</t>
+        </is>
+      </c>
+      <c r="J112" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>iVA TEK</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Full-Stack / Backend Developer</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G113" s="14">
+        <f>HYPERLINK("https://to.indeed.com/aabjskzjgz72","Apply")</f>
+        <v/>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>★ Pan-India Remote</t>
+        </is>
+      </c>
+      <c r="J113" s="13" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr)</t>
         </is>
       </c>
     </row>
@@ -4562,245 +6644,2144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Total openings tracked</t>
-        </is>
-      </c>
-      <c r="B2" s="7">
-        <f>COUNTA('Hiring Companies'!B2:B250)</f>
-        <v/>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>PRIORITY LIST — Python Backend Developer (~4 yr) · Tight match + Ideal fit</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Unique companies</t>
-        </is>
-      </c>
-      <c r="B3" s="7">
-        <f>SUMPRODUCT(1/COUNTIF('Hiring Companies'!B2:B250,'Hiring Companies'!B2:B250))</f>
-        <v/>
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Role / Title</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>Posted</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>Exp Fit</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Apply</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Tight matches</t>
-        </is>
-      </c>
-      <c r="B4" s="7">
-        <f>COUNTIF('Hiring Companies'!H2:H250,"Tight")</f>
+      <c r="A4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Hashone Careers</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Backend AI Developer (Rust, Python)</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I4" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aanlxgttm7fr","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Reasonable matches</t>
-        </is>
-      </c>
-      <c r="B5" s="7">
-        <f>COUNTIF('Hiring Companies'!H2:H250,"Reasonable")</f>
+      <c r="A5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Garuda Spacex Technologies</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer / Backend Analytics</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I5" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aatnn9slnm9v","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Loose matches</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>COUNTIF('Hiring Companies'!H2:H250,"Loose")</f>
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Echotech</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I6" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aarbwym9kqst","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Enfec Solutions</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I7" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aamzhhzkm7cy","Apply")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Voicedots Infotech</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I8" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa9sr8s4679r","Apply")</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
-      <c r="B9" s="7">
-        <f>COUNTIF('Hiring Companies'!E2:E250,"Indeed")</f>
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>YMinds.AI</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer - AI/ML (4+ yrs)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I9" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-python-backend-developer-ai-ml-4+-years-experience-immediate-joiner-remote-at-yminds-ai-4387945955","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>COUNTIF('Hiring Companies'!E2:E250,"LinkedIn")</f>
+      <c r="A10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>6sense</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Python Developer - Backend (Remote)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I10" s="24">
+        <f>HYPERLINK("https://cutshort.io/job/Python-Developer-Backend-6sense-z5mniNnd","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Cutshort</t>
-        </is>
-      </c>
-      <c r="B11" s="7">
-        <f>COUNTIF('Hiring Companies'!E2:E250,"Cutshort")</f>
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Skyloov Property Portal</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I11" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aashyhnzhqkz","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Naukri</t>
-        </is>
-      </c>
-      <c r="B12" s="7">
-        <f>COUNTIF('Hiring Companies'!E2:E250,"Naukri")</f>
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Devstree IT Services</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I12" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa2ttnkbpqlp","Apply")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>HelixBeat</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Senior Engineer — Python, Django/FastAPI, Airflow/PySpark</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I13" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aaywk8glgdcn","Apply")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Immersive Infotech</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I14" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aafcbjmfzrcx","Apply")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Team HR</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I15" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa9xxlv6p6cv","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Halliburton</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Backend Developer (K3S/K8S/Docker)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Bangalore")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I16" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aaqt7ypn7blw","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>nference</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I17" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aahslp4q7jg9","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Solutionchamps Technologies</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer (React Exposure)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I18" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aajxp9vgdy6r","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Roanuz</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I19" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aazk7dyflt8g","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>CivicDataLab</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I20" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aaxn4cn26j8h","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>DDiSmart</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Hyderabad")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="B17" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Delhi")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Chandigarh</t>
-        </is>
-      </c>
-      <c r="B18" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Chandigarh")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I21" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa6thgmyzqtv","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>In2IT Enterprise</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I22" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aad7h4crbjcg","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Sketchwire</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer - Python</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Kharar, Punjab</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I23" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aanj2827cdqv","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Python, FastAPI — Agentic AI Platforms</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I24" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aaldrrkds7tm","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>DSMD.inc</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I25" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa2cvvqpwhy2","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>InterProducTec Virtual Labs</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>Navi Mumbai (Airoli)</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I26" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aazghkbhv4s6","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>AppSquadz Software</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Backend &amp; LLM Integration)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I27" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa9ldcdlxgrx","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Pune")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="B20" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Remote")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I28" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aawb6kf28mhg","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>CGI</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python AI Developer</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I29" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aad498th7m8r","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>Onsite/Hybrid</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I30" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa9by7z9mpss","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>TOPS Infosolutions</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I31" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aawmp77n6syr","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Banyan Data Services</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I32" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa7t7l9d87yw","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Valiant Systems</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Chennai (Porur)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I33" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aa89qvp66ggl","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Orangedatatech</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Developer</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>Indore</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I34" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aam7xnvzwddq","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>Infomanav</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Sr. Python Developer (Django)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Mumbai / Nashik</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I35" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aapyv4twsn8x","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>Avya Technology</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>AI Agentic Engineer / AI Developer</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I36" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aamxxxbfvcyd","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Rhosigma Engineering</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python/Django Developer</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Thane, Mumbai</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I37" s="24">
+        <f>HYPERLINK("https://to.indeed.com/aamj229l4qh6","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>HireTo Co.</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"India")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Kharar, Punjab</t>
-        </is>
-      </c>
-      <c r="B22" s="7">
-        <f>COUNTIF('Hiring Companies'!D2:D250,"Kharar, Punjab")</f>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I38" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Solvex Solutions</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I39" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Hexatic</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I40" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>VGreen Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I41" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Schneider Electric</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I42" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Arctic Wolf</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Senior Backend Developer Python/Django</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I43" s="24">
+        <f>HYPERLINK("https://in.linkedin.com/jobs/senior-backend-developer-python-django-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>vueverse</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I44" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Infomanav</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I45" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>SolutionChamps DesignLabs</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I46" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Syneos Health</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I47" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Intellectsoft</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I48" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Dataviv Technologies</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I49" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>ChicMic Studios</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>Tight</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="I50" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-developer-jobs","Apply")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4811,7 +8792,609 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>LIVE JOB-SEARCH LINKS — Python Backend Developer (4 yr) · India</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Click "Open Search" to run a pre-filled, live search on each site. (Some need login: LinkedIn, Instahyre, Wellfound.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>What it searches</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Open Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer · India · Mid-Senior</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>Best for network + recruiters</t>
+        </is>
+      </c>
+      <c r="E5" s="24">
+        <f>HYPERLINK("https://www.linkedin.com/jobs/search/?keywords=Senior%20Python%20Backend%20Developer&amp;location=India&amp;f_E=3%2C4&amp;f_TPR=r604800","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn (Remote)</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Python Backend Developer · India · Remote</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Remote-only filter (f_WT=2)</t>
+        </is>
+      </c>
+      <c r="E6" s="24">
+        <f>HYPERLINK("https://www.linkedin.com/jobs/search/?keywords=Python%20Backend%20Developer&amp;location=India&amp;f_E=3%2C4&amp;f_WT=2","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Naukri</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer · 4 yr exp</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>India’s biggest job board</t>
+        </is>
+      </c>
+      <c r="E7" s="24">
+        <f>HYPERLINK("https://www.naukri.com/senior-python-backend-developer-jobs?experience=4","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Naukri (Remote)</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Python Backend Developer · Remote</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>Remote roles on Naukri</t>
+        </is>
+      </c>
+      <c r="E8" s="24">
+        <f>HYPERLINK("https://www.naukri.com/python-backend-developer-jobs?wfhType=1","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Indeed India</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer · India</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Broad aggregator</t>
+        </is>
+      </c>
+      <c r="E9" s="24">
+        <f>HYPERLINK("https://in.indeed.com/jobs?q=Senior+Python+Backend+Developer&amp;l=India","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Indeed (Remote)</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Python Backend Developer · Remote</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>Remote-only</t>
+        </is>
+      </c>
+      <c r="E10" s="24">
+        <f>HYPERLINK("https://in.indeed.com/jobs?q=Python+Backend+Developer&amp;l=Remote","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>Instahyre</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>Curated, recruiter-reachout (login)</t>
+        </is>
+      </c>
+      <c r="E11" s="24">
+        <f>HYPERLINK("https://www.instahyre.com/search-jobs/?q=Python+Backend+Developer","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Cutshort</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>AI-matched startup roles</t>
+        </is>
+      </c>
+      <c r="E12" s="24">
+        <f>HYPERLINK("https://cutshort.io/jobs/senior-python-backend-developer-jobs","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Hirist</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>Python Backend Developer</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>Tech-only India job board</t>
+        </is>
+      </c>
+      <c r="E13" s="24">
+        <f>HYPERLINK("https://www.hirist.tech/search/python-backend-developer-jobs","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Wellfound</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Backend Engineer (Python) · startups</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>AngelList startup jobs (login)</t>
+        </is>
+      </c>
+      <c r="E14" s="24">
+        <f>HYPERLINK("https://wellfound.com/role/r/backend-engineer","Open Search")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Total openings tracked</t>
+        </is>
+      </c>
+      <c r="B2" s="7">
+        <f>COUNTA('Hiring Companies'!B2:B250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Unique companies</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>SUMPRODUCT(1/COUNTIF('Hiring Companies'!B2:B250,'Hiring Companies'!B2:B250))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Tight matches</t>
+        </is>
+      </c>
+      <c r="B4" s="7">
+        <f>COUNTIF('Hiring Companies'!H2:H250,"Tight")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Reasonable matches</t>
+        </is>
+      </c>
+      <c r="B5" s="7">
+        <f>COUNTIF('Hiring Companies'!H2:H250,"Reasonable")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Loose matches</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>COUNTIF('Hiring Companies'!H2:H250,"Loose")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>COUNTIF('Hiring Companies'!E2:E250,"Indeed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>COUNTIF('Hiring Companies'!E2:E250,"LinkedIn")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Cutshort</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>COUNTIF('Hiring Companies'!E2:E250,"Cutshort")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Naukri</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>COUNTIF('Hiring Companies'!E2:E250,"Naukri")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Bangalore")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Hyderabad")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="B17" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Delhi")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Chandigarh")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Pune")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Remote")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"India")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Kharar, Punjab</t>
+        </is>
+      </c>
+      <c r="B22" s="7">
+        <f>COUNTIF('Hiring Companies'!D2:D250,"Kharar, Punjab")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Experience fit (4-yr profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ideal (3-6 yr) — your level</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>COUNTIF('Hiring Companies'!K2:K250,"Ideal (3-6 yr)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Stretch (lead / 8+ yr)</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>COUNTIF('Hiring Companies'!K2:K250,"Stretch (lead/8+)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Below (jr / intern)</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>COUNTIF('Hiring Companies'!K2:K250,"Below (jr/intern)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PRIORITY (Tight + Ideal)</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>COUNTIFS('Hiring Companies'!H2:H250,"Tight",'Hiring Companies'!K2:K250,"Ideal (3-6 yr)")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4938,11 +9521,17 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Refreshed via Indeed job API on 2026-06-18 — added 29 current openings (Remote + Delhi NCR + Bangalore + Hyderabad + Pune). New rows highlighted amber; Mode column added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pan-India refresh on 2026-08-04 — added 29 Senior Python Backend roles across Chennai, Mumbai, Kolkata, Ahmedabad, Jaipur, Indore, Coimbatore &amp; Remote (light-blue rows). Apply links use =HYPERLINK().</t>
         </is>
       </c>
     </row>
